--- a/league_dict.xlsx
+++ b/league_dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/557e8c8e9b1f0372/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{C8681A98-ADEC-40B5-AA10-39DA2514FCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{989B4816-950F-43F9-8510-C169B3C9F0A1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{571EE6A4-35FC-4FA1-822A-E53FDFAA9470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E870964E-72B7-432A-AC57-81E8B1FB7B9A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Season</t>
   </si>
@@ -44,37 +44,16 @@
     <t>seasonid</t>
   </si>
   <si>
-    <t>Premier League</t>
-  </si>
-  <si>
     <t>Competition</t>
   </si>
   <si>
-    <t>51r6ph2woavlbbpk8f29nynf8</t>
-  </si>
-  <si>
-    <t>2025/26</t>
-  </si>
-  <si>
     <t>fmid</t>
   </si>
   <si>
-    <t>2024/25</t>
-  </si>
-  <si>
-    <t>2023/24</t>
-  </si>
-  <si>
-    <t>2022/23</t>
-  </si>
-  <si>
-    <t>9n12waklv005j8r32sfjj2eqc</t>
-  </si>
-  <si>
-    <t>1jt5mxgn4q5r6mknmlqv5qjh0</t>
-  </si>
-  <si>
-    <t>80foo89mm28qjvyhjzlpwj28k</t>
+    <t>873cbl9cd9butm4air0mugxzo</t>
+  </si>
+  <si>
+    <t>FIFA World Cup</t>
   </si>
 </sst>
 </file>
@@ -452,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673AED86-F034-49DA-B6EF-799C1DFCCB2C}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -464,69 +443,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
+      <c r="A2">
+        <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
         <v>4</v>
-      </c>
-      <c r="D5">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
